--- a/source_data/Fig6.xlsx
+++ b/source_data/Fig6.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,10 +535,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>imports_replaced_2pct_gdp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>imports_replaced_3pct_gdp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gdp_2030_bn_usd</t>
         </is>
@@ -577,6 +582,9 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
         <v>1974.04</v>
       </c>
     </row>
@@ -613,6 +621,9 @@
         <v>100</v>
       </c>
       <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
         <v>395.29</v>
       </c>
     </row>
@@ -649,6 +660,9 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K4" t="n">
         <v>2554.42</v>
       </c>
     </row>
@@ -685,6 +699,9 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" t="n">
         <v>1859.15</v>
       </c>
     </row>
@@ -718,9 +735,12 @@
         <v>54.59</v>
       </c>
       <c r="I6" t="n">
+        <v>86</v>
+      </c>
+      <c r="J6" t="n">
         <v>100</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>497.44</v>
       </c>
     </row>
@@ -757,6 +777,9 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" t="n">
         <v>466.6</v>
       </c>
     </row>
@@ -790,9 +813,12 @@
         <v>42.51</v>
       </c>
       <c r="I8" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="J8" t="n">
         <v>96.84</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>459.28</v>
       </c>
     </row>
@@ -826,9 +852,12 @@
         <v>37.55</v>
       </c>
       <c r="I9" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="J9" t="n">
         <v>98.81</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>172.02</v>
       </c>
     </row>
@@ -862,9 +891,12 @@
         <v>35.25</v>
       </c>
       <c r="I10" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>81.78</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>225.32</v>
       </c>
     </row>
@@ -898,9 +930,12 @@
         <v>27.98</v>
       </c>
       <c r="I11" t="n">
+        <v>52.41</v>
+      </c>
+      <c r="J11" t="n">
         <v>72.31</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>24.43</v>
       </c>
     </row>
@@ -937,6 +972,9 @@
         <v>69.14</v>
       </c>
       <c r="J12" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="K12" t="n">
         <v>5527.87</v>
       </c>
     </row>
@@ -973,6 +1011,9 @@
         <v>85.66</v>
       </c>
       <c r="J13" t="n">
+        <v>85.66</v>
+      </c>
+      <c r="K13" t="n">
         <v>23607.66</v>
       </c>
     </row>
@@ -1009,6 +1050,9 @@
         <v>43.5</v>
       </c>
       <c r="J14" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K14" t="n">
         <v>625.1</v>
       </c>
     </row>
@@ -1045,6 +1089,9 @@
         <v>29.03</v>
       </c>
       <c r="J15" t="n">
+        <v>29.03</v>
+      </c>
+      <c r="K15" t="n">
         <v>740.9299999999999</v>
       </c>
     </row>
@@ -1081,6 +1128,9 @@
         <v>28.21</v>
       </c>
       <c r="J16" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="K16" t="n">
         <v>710.98</v>
       </c>
     </row>
@@ -1117,6 +1167,9 @@
         <v>15.2</v>
       </c>
       <c r="J17" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K17" t="n">
         <v>798.66</v>
       </c>
     </row>
@@ -1153,6 +1206,9 @@
         <v>12</v>
       </c>
       <c r="J18" t="n">
+        <v>12</v>
+      </c>
+      <c r="K18" t="n">
         <v>130.13</v>
       </c>
     </row>
@@ -1189,6 +1245,9 @@
         <v>11.94</v>
       </c>
       <c r="J19" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="K19" t="n">
         <v>2636.87</v>
       </c>
     </row>
@@ -1225,6 +1284,9 @@
         <v>10.13</v>
       </c>
       <c r="J20" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="K20" t="n">
         <v>2094.53</v>
       </c>
     </row>
@@ -1261,6 +1323,9 @@
         <v>7.81</v>
       </c>
       <c r="J21" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="K21" t="n">
         <v>1181.85</v>
       </c>
     </row>
@@ -1297,6 +1362,9 @@
         <v>4.11</v>
       </c>
       <c r="J22" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="K22" t="n">
         <v>2116.22</v>
       </c>
     </row>
@@ -1333,6 +1401,9 @@
         <v>4.26</v>
       </c>
       <c r="J23" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="K23" t="n">
         <v>4578.91</v>
       </c>
     </row>
@@ -1369,6 +1440,9 @@
         <v>3.45</v>
       </c>
       <c r="J24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K24" t="n">
         <v>159.69</v>
       </c>
     </row>
@@ -1405,6 +1479,9 @@
         <v>3.15</v>
       </c>
       <c r="J25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K25" t="n">
         <v>5313.77</v>
       </c>
     </row>
@@ -1441,6 +1518,9 @@
         <v>3.13</v>
       </c>
       <c r="J26" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="K26" t="n">
         <v>1424.48</v>
       </c>
     </row>
@@ -1477,6 +1557,9 @@
         <v>5.24</v>
       </c>
       <c r="J27" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K27" t="n">
         <v>4290.7</v>
       </c>
     </row>
@@ -1508,7 +1591,8 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
         <v>1494.31</v>
       </c>
     </row>
@@ -1540,7 +1624,8 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
         <v>563.9299999999999</v>
       </c>
     </row>
@@ -1572,7 +1657,8 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
         <v>34105.33</v>
       </c>
     </row>
@@ -1604,7 +1690,8 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
         <v>126.68</v>
       </c>
     </row>
